--- a/fig1/FIG1.xlsx
+++ b/fig1/FIG1.xlsx
@@ -4,12 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18900" windowHeight="13284" activeTab="2"/>
+    <workbookView windowWidth="18900" windowHeight="13284" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="FIG1E" sheetId="1" r:id="rId1"/>
-    <sheet name="FIG 1C" sheetId="2" r:id="rId2"/>
-    <sheet name="FIG1D" sheetId="3" r:id="rId3"/>
+    <sheet name="FIG 1C" sheetId="2" r:id="rId1"/>
+    <sheet name="FIG1D" sheetId="3" r:id="rId2"/>
+    <sheet name="FIG1E" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,30 +30,6 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="20">
-  <si>
-    <t>B-healthy</t>
-  </si>
-  <si>
-    <t>B-ST</t>
-  </si>
-  <si>
-    <t>T-healthy</t>
-  </si>
-  <si>
-    <t>T-ST</t>
-  </si>
-  <si>
-    <t>NK-healthy</t>
-  </si>
-  <si>
-    <t>NK-ST</t>
-  </si>
-  <si>
-    <t>Myeloid-healthy</t>
-  </si>
-  <si>
-    <t>Myeloid-ST</t>
-  </si>
   <si>
     <t>percent</t>
   </si>
@@ -89,6 +65,30 @@
   </si>
   <si>
     <t>celltype</t>
+  </si>
+  <si>
+    <t>B-healthy</t>
+  </si>
+  <si>
+    <t>B-ST</t>
+  </si>
+  <si>
+    <t>T-healthy</t>
+  </si>
+  <si>
+    <t>T-ST</t>
+  </si>
+  <si>
+    <t>NK-healthy</t>
+  </si>
+  <si>
+    <t>NK-ST</t>
+  </si>
+  <si>
+    <t>Myeloid-healthy</t>
+  </si>
+  <si>
+    <t>Myeloid-ST</t>
   </si>
 </sst>
 </file>
@@ -714,10 +714,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1243,13 +1243,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
-  <cols>
-    <col min="1" max="8" width="14.2222222222222"/>
-  </cols>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1259,228 +1256,115 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="2">
+        <v>0.127250225022502</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="2">
+        <v>0.185568556855686</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="2">
+        <v>0.0981473147314731</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="2">
+        <v>0.00532553255325533</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="1">
-        <v>0.169</v>
-      </c>
-      <c r="B2" s="1">
-        <v>0.0495</v>
-      </c>
-      <c r="C2" s="1">
-        <v>0.651</v>
-      </c>
-      <c r="D2" s="1">
-        <v>0.816</v>
-      </c>
-      <c r="E2" s="1">
-        <v>0.069696</v>
-      </c>
-      <c r="F2" s="1">
-        <v>0.0442</v>
-      </c>
-      <c r="G2" s="1">
-        <v>0.084629641</v>
-      </c>
-      <c r="H2" s="1">
-        <v>0.081996012</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="1">
-        <v>0.168</v>
-      </c>
-      <c r="B3" s="1">
-        <v>0.126</v>
-      </c>
-      <c r="C3" s="1">
-        <v>0.663</v>
-      </c>
-      <c r="D3" s="1">
-        <v>0.657</v>
-      </c>
-      <c r="E3" s="1">
-        <v>0.042585</v>
-      </c>
-      <c r="F3" s="1">
-        <v>0.115856</v>
-      </c>
-      <c r="G3" s="1">
-        <v>0.215433124</v>
-      </c>
-      <c r="H3" s="1">
-        <v>0.233543352</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="1">
-        <v>0.0775</v>
-      </c>
-      <c r="B4" s="1">
-        <v>0.0421</v>
-      </c>
-      <c r="C4" s="1">
-        <v>0.741</v>
-      </c>
-      <c r="D4" s="1">
-        <v>0.671</v>
-      </c>
-      <c r="E4" s="1">
-        <v>0.126732</v>
-      </c>
-      <c r="F4" s="1">
-        <v>0.148292</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0.066296674</v>
-      </c>
-      <c r="H4" s="1">
-        <v>0.158280936</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="1">
-        <v>0.0879</v>
-      </c>
-      <c r="B5" s="1">
-        <v>0.199</v>
-      </c>
-      <c r="C5" s="1">
-        <v>0.733</v>
-      </c>
-      <c r="D5" s="1">
-        <v>0.716</v>
-      </c>
-      <c r="E5" s="1">
-        <v>0.1036</v>
-      </c>
-      <c r="F5" s="1">
-        <v>0.01728</v>
-      </c>
-      <c r="G5" s="1">
-        <v>0.13715928</v>
-      </c>
-      <c r="H5" s="1">
-        <v>0.12725328</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="1">
-        <v>0.165</v>
-      </c>
-      <c r="B6" s="1">
-        <v>0.0317</v>
-      </c>
-      <c r="C6" s="1">
-        <v>0.627</v>
-      </c>
-      <c r="D6" s="1">
-        <v>0.732</v>
-      </c>
-      <c r="E6" s="1">
-        <v>0.098195</v>
-      </c>
-      <c r="F6" s="1">
-        <v>0.057981</v>
-      </c>
-      <c r="G6" s="1">
-        <v>0.167885739</v>
-      </c>
-      <c r="H6" s="1">
-        <v>0.057487693</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="1">
-        <v>0.184</v>
-      </c>
-      <c r="B7" s="1">
-        <v>0.0349</v>
-      </c>
-      <c r="C7" s="1">
-        <v>0.712</v>
-      </c>
-      <c r="D7" s="1">
-        <v>0.771</v>
-      </c>
-      <c r="E7" s="1">
-        <v>0.017748</v>
-      </c>
-      <c r="F7" s="1">
-        <v>0.08415</v>
-      </c>
-      <c r="G7" s="1">
-        <v>0.060278954</v>
-      </c>
-      <c r="H7" s="1">
-        <v>0.197138832</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="1">
-        <v>0.219</v>
-      </c>
-      <c r="B8" s="1">
-        <v>0.162</v>
-      </c>
-      <c r="C8" s="1">
-        <v>0.631</v>
-      </c>
-      <c r="D8" s="1">
-        <v>0.471</v>
-      </c>
-      <c r="E8" s="1">
-        <v>0.02059</v>
-      </c>
-      <c r="F8" s="1">
-        <v>0.11916</v>
-      </c>
-      <c r="G8" s="1">
-        <v>0.12054965</v>
-      </c>
-      <c r="H8" s="1">
-        <v>0.109671165</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="1">
-        <v>0.251</v>
-      </c>
-      <c r="B9" s="1">
-        <v>0.067</v>
-      </c>
-      <c r="C9" s="1">
-        <v>0.646</v>
-      </c>
-      <c r="D9" s="1">
-        <v>0.528</v>
-      </c>
-      <c r="E9" s="1">
-        <v>0.026928</v>
-      </c>
-      <c r="F9" s="1">
-        <v>0.043179</v>
-      </c>
-      <c r="G9" s="1">
-        <v>0.07937643</v>
-      </c>
-      <c r="H9" s="1">
-        <v>0.215333664</v>
+    <row r="6" spans="1:3">
+      <c r="A6" s="2">
+        <v>0.583708370837084</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="2">
+        <v>0.0349259408679615</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="2">
+        <v>0.332286323554838</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="2">
+        <v>0.0865079822488617</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="2">
+        <v>0.0303152556048643</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="2">
+        <v>0.515964497723474</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1492,128 +1376,513 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="2">
+        <v>0.148994875837603</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="2">
+        <v>0.215346209433714</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="2">
+        <v>0.0836946524766785</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="2">
+        <v>0.0147155432926028</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="2">
+        <v>0.537248718959401</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1">
-        <v>0.127250225022502</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1">
-        <v>0.185568556855686</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1">
-        <v>0.0981473147314731</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1">
-        <v>0.00532553255325533</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1">
-        <v>0.583708370837084</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>16</v>
+      <c r="C6" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="1">
-        <v>0.0349259408679615</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>12</v>
+      <c r="A7" s="2">
+        <v>0.0813953488372093</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="1">
-        <v>0.332286323554838</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>13</v>
+      <c r="A8" s="2">
+        <v>0.173211935059237</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="1">
-        <v>0.0865079822488617</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>14</v>
+      <c r="A9" s="2">
+        <v>0.0544098288723124</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="1">
-        <v>0.0303152556048643</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>15</v>
+      <c r="A10" s="2">
+        <v>0.000877577885037297</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="1">
-        <v>0.515964497723474</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>16</v>
+      <c r="A11" s="2">
+        <v>0.690105309346205</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="2">
+        <v>0.152661769145617</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="2">
+        <v>0.174096809902385</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="2">
+        <v>0.149340847338231</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="2">
+        <v>0.00221394787159102</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="2">
+        <v>0.521686625742176</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="2">
+        <v>0.0226213481868819</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="2">
+        <v>0.220188700693418</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="2">
+        <v>0.0641127657155849</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="2">
+        <v>0.0178469932931681</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="2">
+        <v>0.675230192110947</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="2">
+        <v>0.050710718401844</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="2">
+        <v>0.0136381098732232</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="2">
+        <v>0.108912792931233</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="2">
+        <v>0.3267383787937</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="2">
+        <v>0.0190238782471792</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="2">
+        <v>0.321962739438468</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="2">
+        <v>0.119260036735765</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="2">
+        <v>0.0124639202309105</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="2">
+        <v>0.527289425347678</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="2">
+        <v>0.0634799235181644</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="2">
+        <v>0.408795411089866</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="2">
+        <v>0.111472275334608</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="2">
+        <v>0.0248565965583174</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" s="2">
+        <v>0.391395793499044</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="2">
+        <v>0.0206289308176101</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" s="2">
+        <v>0.25937106918239</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" s="2">
+        <v>0.123018867924528</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" s="2">
+        <v>0.0188679245283019</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" s="2">
+        <v>0.57811320754717</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" s="2">
+        <v>0.0490702479338843</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" s="2">
+        <v>0.353305785123967</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" s="2">
+        <v>0.0996900826446281</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" s="2">
+        <v>0.00723140495867769</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" s="2">
+        <v>0.490702479338843</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1625,513 +1894,244 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C46"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="8" width="14.2222222222222"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1">
-        <v>0.148994875837603</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1">
-        <v>0.215346209433714</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1">
-        <v>0.0836946524766785</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1">
-        <v>0.0147155432926028</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1">
-        <v>0.537248718959401</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1">
-        <v>0.0813953488372093</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1">
-        <v>0.173211935059237</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1">
-        <v>0.0544098288723124</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1">
-        <v>0.000877577885037297</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="1">
-        <v>0.690105309346205</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="1">
-        <v>0.152661769145617</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="1">
-        <v>0.174096809902385</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="1">
-        <v>0.149340847338231</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="1">
-        <v>0.00221394787159102</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="1">
-        <v>0.521686625742176</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="1">
-        <v>0.0226213481868819</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="1">
-        <v>0.220188700693418</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="1">
-        <v>0.0641127657155849</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="1">
-        <v>0.0178469932931681</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="1">
-        <v>0.675230192110947</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="1">
-        <v>0.050710718401844</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="1">
-        <v>0.0136381098732232</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="1">
-        <v>0.108912792931233</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="1">
-        <v>0.3267383787937</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="1">
-        <v>0.0190238782471792</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="1">
-        <v>0.321962739438468</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="1">
-        <v>0.119260036735765</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="1">
-        <v>0.0124639202309105</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="1">
-        <v>0.527289425347678</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="1">
-        <v>0.0634799235181644</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="1">
-        <v>0.408795411089866</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="1">
-        <v>0.111472275334608</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="1">
-        <v>0.0248565965583174</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="1">
-        <v>0.391395793499044</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" s="1">
-        <v>0.0206289308176101</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" s="1">
-        <v>0.25937106918239</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="1">
-        <v>0.123018867924528</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" s="1">
-        <v>0.0188679245283019</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" s="1">
-        <v>0.57811320754717</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" s="1">
-        <v>0.0490702479338843</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" s="1">
-        <v>0.353305785123967</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" s="1">
-        <v>0.0996900826446281</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" s="1">
-        <v>0.00723140495867769</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="1">
-        <v>0.490702479338843</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>17</v>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="2">
+        <v>0.169</v>
+      </c>
+      <c r="B2" s="2">
+        <v>0.0495</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0.651</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0.816</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0.069696</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0.0442</v>
+      </c>
+      <c r="G2" s="2">
+        <v>0.084629641</v>
+      </c>
+      <c r="H2" s="2">
+        <v>0.081996012</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="2">
+        <v>0.168</v>
+      </c>
+      <c r="B3" s="2">
+        <v>0.126</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0.663</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0.657</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0.042585</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0.115856</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0.215433124</v>
+      </c>
+      <c r="H3" s="2">
+        <v>0.233543352</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="2">
+        <v>0.0775</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0.0421</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0.741</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0.671</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0.126732</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.148292</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0.066296674</v>
+      </c>
+      <c r="H4" s="2">
+        <v>0.158280936</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="2">
+        <v>0.0879</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0.199</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0.733</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0.716</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0.1036</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.01728</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0.13715928</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0.12725328</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="2">
+        <v>0.165</v>
+      </c>
+      <c r="B6" s="2">
+        <v>0.0317</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0.627</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0.732</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0.098195</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.057981</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0.167885739</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0.057487693</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="2">
+        <v>0.184</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0.0349</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0.712</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0.771</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0.017748</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.08415</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0.060278954</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0.197138832</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="2">
+        <v>0.219</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0.162</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0.631</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0.471</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0.02059</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.11916</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0.12054965</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0.109671165</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="2">
+        <v>0.251</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0.067</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0.646</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0.528</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0.026928</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.043179</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0.07937643</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0.215333664</v>
       </c>
     </row>
   </sheetData>
